--- a/artfynd/A 10625-2024 artfynd.xlsx
+++ b/artfynd/A 10625-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117965523</v>
+        <v>117966965</v>
       </c>
       <c r="B2" t="n">
         <v>78217</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Vitmossaflon (Vitmossaflon), Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592347</v>
+        <v>592168</v>
       </c>
       <c r="R2" t="n">
-        <v>6983195</v>
+        <v>6983049</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117965190</v>
+        <v>117963021</v>
       </c>
       <c r="B3" t="n">
-        <v>97836</v>
+        <v>57287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,30 +799,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592393</v>
+        <v>592642</v>
       </c>
       <c r="R3" t="n">
-        <v>6983227</v>
+        <v>6982779</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117962951</v>
+        <v>117965382</v>
       </c>
       <c r="B4" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,34 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Vitmossaflon (Vitmossaflon), Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592630</v>
+        <v>592350</v>
       </c>
       <c r="R4" t="n">
-        <v>6982740</v>
+        <v>6983237</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117967006</v>
+        <v>117965168</v>
       </c>
       <c r="B5" t="n">
-        <v>56499</v>
+        <v>97836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,36 +1028,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1065,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592211</v>
+        <v>592400</v>
       </c>
       <c r="R5" t="n">
-        <v>6983013</v>
+        <v>6983226</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117965084</v>
+        <v>117962951</v>
       </c>
       <c r="B6" t="n">
-        <v>79561</v>
+        <v>79098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592497</v>
+        <v>592630</v>
       </c>
       <c r="R6" t="n">
-        <v>6983185</v>
+        <v>6982740</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117965048</v>
+        <v>117965190</v>
       </c>
       <c r="B7" t="n">
-        <v>56499</v>
+        <v>97836</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,31 +1256,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1294,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592470</v>
+        <v>592393</v>
       </c>
       <c r="R7" t="n">
-        <v>6983180</v>
+        <v>6983227</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117965787</v>
+        <v>117967227</v>
       </c>
       <c r="B8" t="n">
-        <v>78216</v>
+        <v>78217</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,34 +1376,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vitmossaflon (Vitmossaflon), Jmt</t>
+          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592222</v>
+        <v>592271</v>
       </c>
       <c r="R8" t="n">
-        <v>6983253</v>
+        <v>6982856</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117965382</v>
+        <v>117962937</v>
       </c>
       <c r="B9" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,34 +1488,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vitmossaflon (Vitmossaflon), Jmt</t>
+          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592350</v>
+        <v>592630</v>
       </c>
       <c r="R9" t="n">
-        <v>6983237</v>
+        <v>6982740</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,22 +1572,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117967227</v>
+        <v>117967045</v>
       </c>
       <c r="B10" t="n">
-        <v>78217</v>
+        <v>78125</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,34 +1600,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
+          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592271</v>
+        <v>592243</v>
       </c>
       <c r="R10" t="n">
-        <v>6982856</v>
+        <v>6982968</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,22 +1684,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117966965</v>
+        <v>117965048</v>
       </c>
       <c r="B11" t="n">
-        <v>78217</v>
+        <v>56499</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,38 +1708,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vitmossaflon (Vitmossaflon), Jmt</t>
+          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592168</v>
+        <v>592470</v>
       </c>
       <c r="R11" t="n">
-        <v>6983049</v>
+        <v>6983180</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,22 +1801,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117962937</v>
+        <v>117965787</v>
       </c>
       <c r="B12" t="n">
-        <v>78217</v>
+        <v>78216</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,34 +1829,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Vitmossaflon (Vitmossaflon), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592630</v>
+        <v>592222</v>
       </c>
       <c r="R12" t="n">
-        <v>6982740</v>
+        <v>6983253</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1888,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1898,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117963021</v>
+        <v>117964775</v>
       </c>
       <c r="B13" t="n">
-        <v>57287</v>
+        <v>78217</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,42 +1941,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592642</v>
+        <v>592497</v>
       </c>
       <c r="R13" t="n">
-        <v>6982779</v>
+        <v>6983093</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2006,7 +2000,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2016,7 +2010,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2043,10 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117967045</v>
+        <v>117967006</v>
       </c>
       <c r="B14" t="n">
-        <v>78125</v>
+        <v>56499</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,41 +2049,51 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592243</v>
+        <v>592211</v>
       </c>
       <c r="R14" t="n">
-        <v>6982968</v>
+        <v>6983013</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2118,7 +2122,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2128,7 +2132,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,7 +2159,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117964775</v>
+        <v>117963859</v>
       </c>
       <c r="B15" t="n">
         <v>78217</v>
@@ -2195,10 +2199,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592497</v>
+        <v>592568</v>
       </c>
       <c r="R15" t="n">
-        <v>6983093</v>
+        <v>6982951</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2230,7 +2234,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2240,7 +2244,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117964752</v>
+        <v>117965084</v>
       </c>
       <c r="B16" t="n">
-        <v>91962</v>
+        <v>79561</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,21 +2287,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2307,10 +2311,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592509</v>
+        <v>592497</v>
       </c>
       <c r="R16" t="n">
-        <v>6983102</v>
+        <v>6983185</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2342,7 +2346,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2352,7 +2356,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2367,19 +2371,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117963859</v>
+        <v>117965523</v>
       </c>
       <c r="B17" t="n">
         <v>78217</v>
@@ -2419,10 +2423,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592568</v>
+        <v>592347</v>
       </c>
       <c r="R17" t="n">
-        <v>6982951</v>
+        <v>6983195</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,7 +2458,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2464,7 +2468,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,10 +2495,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117964835</v>
+        <v>117964752</v>
       </c>
       <c r="B18" t="n">
-        <v>97753</v>
+        <v>91962</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2503,43 +2507,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592498</v>
+        <v>592509</v>
       </c>
       <c r="R18" t="n">
-        <v>6983096</v>
+        <v>6983102</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2571,7 +2570,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2581,7 +2580,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2596,22 +2595,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117965168</v>
+        <v>117964835</v>
       </c>
       <c r="B19" t="n">
-        <v>97836</v>
+        <v>97753</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2620,30 +2619,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592400</v>
+        <v>592498</v>
       </c>
       <c r="R19" t="n">
-        <v>6983226</v>
+        <v>6983096</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2712,22 +2712,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117980679</v>
+        <v>117980634</v>
       </c>
       <c r="B20" t="n">
-        <v>90648</v>
+        <v>78217</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,25 +2736,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592361</v>
+        <v>592165</v>
       </c>
       <c r="R20" t="n">
-        <v>6983221</v>
+        <v>6983245</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117980591</v>
+        <v>117980583</v>
       </c>
       <c r="B21" t="n">
-        <v>79098</v>
+        <v>90464</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2838,25 +2838,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592624</v>
+        <v>592514</v>
       </c>
       <c r="R21" t="n">
-        <v>6982741</v>
+        <v>6983143</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117980634</v>
+        <v>117980704</v>
       </c>
       <c r="B22" t="n">
-        <v>78217</v>
+        <v>91772</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2940,25 +2940,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592165</v>
+        <v>592312</v>
       </c>
       <c r="R22" t="n">
-        <v>6983245</v>
+        <v>6982911</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3030,10 +3030,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117980583</v>
+        <v>117980612</v>
       </c>
       <c r="B23" t="n">
-        <v>90464</v>
+        <v>56499</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3046,34 +3046,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592514</v>
+        <v>592308</v>
       </c>
       <c r="R23" t="n">
-        <v>6983143</v>
+        <v>6982909</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3132,10 +3140,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117980612</v>
+        <v>117980679</v>
       </c>
       <c r="B24" t="n">
-        <v>56499</v>
+        <v>90648</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3144,46 +3152,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592308</v>
+        <v>592361</v>
       </c>
       <c r="R24" t="n">
-        <v>6982909</v>
+        <v>6983221</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3242,7 +3242,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117980590</v>
+        <v>117980589</v>
       </c>
       <c r="B25" t="n">
         <v>79098</v>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592274</v>
+        <v>592222</v>
       </c>
       <c r="R25" t="n">
-        <v>6983236</v>
+        <v>6983283</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3344,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117980589</v>
+        <v>117980684</v>
       </c>
       <c r="B26" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3360,21 +3360,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3384,10 +3384,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592222</v>
+        <v>592455</v>
       </c>
       <c r="R26" t="n">
-        <v>6983283</v>
+        <v>6983193</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117980704</v>
+        <v>117980591</v>
       </c>
       <c r="B27" t="n">
-        <v>91772</v>
+        <v>79098</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3458,25 +3458,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592312</v>
+        <v>592624</v>
       </c>
       <c r="R27" t="n">
-        <v>6982911</v>
+        <v>6982741</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3548,10 +3548,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117980684</v>
+        <v>117980590</v>
       </c>
       <c r="B28" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3564,21 +3564,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592455</v>
+        <v>592274</v>
       </c>
       <c r="R28" t="n">
-        <v>6983193</v>
+        <v>6983236</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>

--- a/artfynd/A 10625-2024 artfynd.xlsx
+++ b/artfynd/A 10625-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117966965</v>
+        <v>117967045</v>
       </c>
       <c r="B2" t="n">
-        <v>78217</v>
+        <v>78127</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vitmossaflon (Vitmossaflon), Jmt</t>
+          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592168</v>
+        <v>592243</v>
       </c>
       <c r="R2" t="n">
-        <v>6983049</v>
+        <v>6982968</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +775,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,7 +790,7 @@
         <v>117963021</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117965382</v>
+        <v>117963859</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>78219</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vitmossaflon (Vitmossaflon), Jmt</t>
+          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592350</v>
+        <v>592568</v>
       </c>
       <c r="R4" t="n">
-        <v>6983237</v>
+        <v>6982951</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117965168</v>
+        <v>117965523</v>
       </c>
       <c r="B5" t="n">
-        <v>97836</v>
+        <v>78219</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,42 +1028,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592400</v>
+        <v>592347</v>
       </c>
       <c r="R5" t="n">
-        <v>6983226</v>
+        <v>6983195</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117962951</v>
+        <v>117964752</v>
       </c>
       <c r="B6" t="n">
-        <v>79098</v>
+        <v>91964</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592630</v>
+        <v>592509</v>
       </c>
       <c r="R6" t="n">
-        <v>6982740</v>
+        <v>6983102</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,22 +1228,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117965190</v>
+        <v>117967006</v>
       </c>
       <c r="B7" t="n">
-        <v>97836</v>
+        <v>56500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,30 +1252,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1288,13 +1290,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592393</v>
+        <v>592211</v>
       </c>
       <c r="R7" t="n">
-        <v>6983227</v>
+        <v>6983013</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117967227</v>
+        <v>117964775</v>
       </c>
       <c r="B8" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,14 +1398,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
+          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592271</v>
+        <v>592497</v>
       </c>
       <c r="R8" t="n">
-        <v>6982856</v>
+        <v>6983093</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117962937</v>
+        <v>117965190</v>
       </c>
       <c r="B9" t="n">
-        <v>78217</v>
+        <v>97838</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,38 +1486,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592630</v>
+        <v>592393</v>
       </c>
       <c r="R9" t="n">
-        <v>6982740</v>
+        <v>6983227</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,22 +1578,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117967045</v>
+        <v>117966965</v>
       </c>
       <c r="B10" t="n">
-        <v>78125</v>
+        <v>78219</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,34 +1606,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Vitmossaflon (Vitmossaflon), Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592243</v>
+        <v>592168</v>
       </c>
       <c r="R10" t="n">
-        <v>6982968</v>
+        <v>6983049</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,22 +1690,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117965048</v>
+        <v>117965168</v>
       </c>
       <c r="B11" t="n">
-        <v>56499</v>
+        <v>97838</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,31 +1714,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1741,10 +1746,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592470</v>
+        <v>592400</v>
       </c>
       <c r="R11" t="n">
-        <v>6983180</v>
+        <v>6983226</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1791,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,7 +1821,7 @@
         <v>117965787</v>
       </c>
       <c r="B12" t="n">
-        <v>78216</v>
+        <v>78218</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1925,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117964775</v>
+        <v>117965084</v>
       </c>
       <c r="B13" t="n">
-        <v>78217</v>
+        <v>79563</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,21 +1946,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1968,7 +1973,7 @@
         <v>592497</v>
       </c>
       <c r="R13" t="n">
-        <v>6983093</v>
+        <v>6983185</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2000,7 +2005,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2010,7 +2015,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117967006</v>
+        <v>117967227</v>
       </c>
       <c r="B14" t="n">
-        <v>56499</v>
+        <v>78219</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,51 +2054,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592211</v>
+        <v>592271</v>
       </c>
       <c r="R14" t="n">
-        <v>6983013</v>
+        <v>6982856</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2122,7 +2117,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2132,7 +2127,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2147,22 +2142,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117963859</v>
+        <v>117965382</v>
       </c>
       <c r="B15" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,34 +2170,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Vitmossaflon (Vitmossaflon), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592568</v>
+        <v>592350</v>
       </c>
       <c r="R15" t="n">
-        <v>6982951</v>
+        <v>6983237</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2234,7 +2229,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2244,7 +2239,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2259,22 +2254,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117965084</v>
+        <v>117962951</v>
       </c>
       <c r="B16" t="n">
-        <v>79561</v>
+        <v>79100</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,21 +2282,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2311,10 +2306,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592497</v>
+        <v>592630</v>
       </c>
       <c r="R16" t="n">
-        <v>6983185</v>
+        <v>6982740</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2341,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2356,7 +2351,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2383,10 +2378,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117965523</v>
+        <v>117964835</v>
       </c>
       <c r="B17" t="n">
-        <v>78217</v>
+        <v>97755</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2395,38 +2390,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592347</v>
+        <v>592498</v>
       </c>
       <c r="R17" t="n">
-        <v>6983195</v>
+        <v>6983096</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,10 +2495,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117964752</v>
+        <v>117965048</v>
       </c>
       <c r="B18" t="n">
-        <v>91962</v>
+        <v>56500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2507,38 +2507,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592509</v>
+        <v>592470</v>
       </c>
       <c r="R18" t="n">
-        <v>6983102</v>
+        <v>6983180</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2570,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2580,7 +2585,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2607,10 +2612,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117964835</v>
+        <v>117962937</v>
       </c>
       <c r="B19" t="n">
-        <v>97753</v>
+        <v>78219</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2619,43 +2624,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592498</v>
+        <v>592630</v>
       </c>
       <c r="R19" t="n">
-        <v>6983096</v>
+        <v>6982740</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117980634</v>
+        <v>117980590</v>
       </c>
       <c r="B20" t="n">
-        <v>78217</v>
+        <v>79100</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592165</v>
+        <v>592274</v>
       </c>
       <c r="R20" t="n">
-        <v>6983245</v>
+        <v>6983236</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117980583</v>
+        <v>117980684</v>
       </c>
       <c r="B21" t="n">
-        <v>90464</v>
+        <v>78482</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2838,25 +2838,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592514</v>
+        <v>592455</v>
       </c>
       <c r="R21" t="n">
-        <v>6983143</v>
+        <v>6983193</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117980704</v>
+        <v>117980634</v>
       </c>
       <c r="B22" t="n">
-        <v>91772</v>
+        <v>78219</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2940,25 +2940,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592312</v>
+        <v>592165</v>
       </c>
       <c r="R22" t="n">
-        <v>6982911</v>
+        <v>6983245</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3030,10 +3030,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117980612</v>
+        <v>117980591</v>
       </c>
       <c r="B23" t="n">
-        <v>56499</v>
+        <v>79100</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3042,46 +3042,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592308</v>
+        <v>592624</v>
       </c>
       <c r="R23" t="n">
-        <v>6982909</v>
+        <v>6982741</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3140,10 +3132,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117980679</v>
+        <v>117980589</v>
       </c>
       <c r="B24" t="n">
-        <v>90648</v>
+        <v>79100</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3152,25 +3144,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3180,10 +3172,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592361</v>
+        <v>592222</v>
       </c>
       <c r="R24" t="n">
-        <v>6983221</v>
+        <v>6983283</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3242,10 +3234,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117980589</v>
+        <v>117980583</v>
       </c>
       <c r="B25" t="n">
-        <v>79098</v>
+        <v>90466</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3254,25 +3246,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3282,10 +3274,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592222</v>
+        <v>592514</v>
       </c>
       <c r="R25" t="n">
-        <v>6983283</v>
+        <v>6983143</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3344,10 +3336,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117980684</v>
+        <v>117980704</v>
       </c>
       <c r="B26" t="n">
-        <v>78480</v>
+        <v>91774</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3356,25 +3348,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3384,10 +3376,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592455</v>
+        <v>592312</v>
       </c>
       <c r="R26" t="n">
-        <v>6983193</v>
+        <v>6982911</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3446,10 +3438,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117980591</v>
+        <v>117980612</v>
       </c>
       <c r="B27" t="n">
-        <v>79098</v>
+        <v>56500</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3458,38 +3450,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592624</v>
+        <v>592308</v>
       </c>
       <c r="R27" t="n">
-        <v>6982741</v>
+        <v>6982909</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3548,10 +3548,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117980590</v>
+        <v>117980679</v>
       </c>
       <c r="B28" t="n">
-        <v>79098</v>
+        <v>90650</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3560,25 +3560,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592274</v>
+        <v>592361</v>
       </c>
       <c r="R28" t="n">
-        <v>6983236</v>
+        <v>6983221</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>

--- a/artfynd/A 10625-2024 artfynd.xlsx
+++ b/artfynd/A 10625-2024 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117965523</v>
+        <v>117964752</v>
       </c>
       <c r="B5" t="n">
-        <v>78219</v>
+        <v>91964</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592347</v>
+        <v>592509</v>
       </c>
       <c r="R5" t="n">
-        <v>6983195</v>
+        <v>6983102</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117964752</v>
+        <v>117965523</v>
       </c>
       <c r="B6" t="n">
-        <v>91964</v>
+        <v>78219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592509</v>
+        <v>592347</v>
       </c>
       <c r="R6" t="n">
-        <v>6983102</v>
+        <v>6983195</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,12 +1228,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117967227</v>
+        <v>117965382</v>
       </c>
       <c r="B14" t="n">
-        <v>78219</v>
+        <v>78482</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,34 +2058,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
+          <t>Vitmossaflon (Vitmossaflon), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592271</v>
+        <v>592350</v>
       </c>
       <c r="R14" t="n">
-        <v>6982856</v>
+        <v>6983237</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,22 +2142,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117965382</v>
+        <v>117967227</v>
       </c>
       <c r="B15" t="n">
-        <v>78482</v>
+        <v>78219</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2170,34 +2170,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vitmossaflon (Vitmossaflon), Jmt</t>
+          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592350</v>
+        <v>592271</v>
       </c>
       <c r="R15" t="n">
-        <v>6983237</v>
+        <v>6982856</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2254,12 +2254,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117980590</v>
+        <v>117980634</v>
       </c>
       <c r="B20" t="n">
-        <v>79100</v>
+        <v>78219</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592274</v>
+        <v>592165</v>
       </c>
       <c r="R20" t="n">
-        <v>6983236</v>
+        <v>6983245</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117980684</v>
+        <v>117980590</v>
       </c>
       <c r="B21" t="n">
-        <v>78482</v>
+        <v>79100</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2842,21 +2842,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592455</v>
+        <v>592274</v>
       </c>
       <c r="R21" t="n">
-        <v>6983193</v>
+        <v>6983236</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117980634</v>
+        <v>117980684</v>
       </c>
       <c r="B22" t="n">
-        <v>78219</v>
+        <v>78482</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2944,21 +2944,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592165</v>
+        <v>592455</v>
       </c>
       <c r="R22" t="n">
-        <v>6983245</v>
+        <v>6983193</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>

--- a/artfynd/A 10625-2024 artfynd.xlsx
+++ b/artfynd/A 10625-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117965523</v>
+        <v>117967045</v>
       </c>
       <c r="B2" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592347</v>
+        <v>592243</v>
       </c>
       <c r="R2" t="n">
-        <v>6983195</v>
+        <v>6982968</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,70 +770,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117964835</v>
+        <v>117980679</v>
       </c>
       <c r="B3" t="n">
-        <v>97763</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592498</v>
+        <v>592361</v>
       </c>
       <c r="R3" t="n">
-        <v>6983096</v>
+        <v>6983221</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,19 +850,9 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,27 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117965382</v>
+        <v>117964752</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,34 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vitmossaflon (Vitmossaflon), Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592350</v>
+        <v>592509</v>
       </c>
       <c r="R4" t="n">
-        <v>6983237</v>
+        <v>6983102</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +949,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +959,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,15 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117964752</v>
+        <v>117980704</v>
       </c>
       <c r="B5" t="n">
-        <v>91969</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,37 +997,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592509</v>
+        <v>592312</v>
       </c>
       <c r="R5" t="n">
-        <v>6983102</v>
+        <v>6982911</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,19 +1054,9 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,69 +1071,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117965190</v>
+        <v>117980583</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592393</v>
+        <v>592514</v>
       </c>
       <c r="R6" t="n">
-        <v>6983227</v>
+        <v>6983143</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,19 +1151,9 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,65 +1168,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117966965</v>
+        <v>117980584</v>
       </c>
       <c r="B7" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vitmossaflon (Vitmossaflon), Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592168</v>
+        <v>592541</v>
       </c>
       <c r="R7" t="n">
-        <v>6983049</v>
+        <v>6983087</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,19 +1248,9 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,62 +1265,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117962951</v>
+        <v>117965382</v>
       </c>
       <c r="B8" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592630</v>
+        <v>592350</v>
       </c>
       <c r="R8" t="n">
-        <v>6982740</v>
+        <v>6983237</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1347,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1357,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,65 +1372,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117963859</v>
+        <v>117980684</v>
       </c>
       <c r="B9" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592568</v>
+        <v>592455</v>
       </c>
       <c r="R9" t="n">
-        <v>6982951</v>
+        <v>6983193</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1541,19 +1452,9 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,12 +1469,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1583,12 +1484,7 @@
         <v>117965787</v>
       </c>
       <c r="B10" t="n">
-        <v>78220</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1512,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vitmossaflon (Vitmossaflon), Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1692,15 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117967045</v>
+        <v>117962951</v>
       </c>
       <c r="B11" t="n">
-        <v>78129</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,34 +1599,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592243</v>
+        <v>592630</v>
       </c>
       <c r="R11" t="n">
-        <v>6982968</v>
+        <v>6982740</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,7 +1658,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1668,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,27 +1683,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117962937</v>
+        <v>117980589</v>
       </c>
       <c r="B12" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,37 +1706,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592630</v>
+        <v>592222</v>
       </c>
       <c r="R12" t="n">
-        <v>6982740</v>
+        <v>6983283</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1877,19 +1763,9 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,69 +1780,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117965168</v>
+        <v>117980590</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592400</v>
+        <v>592274</v>
       </c>
       <c r="R13" t="n">
-        <v>6983226</v>
+        <v>6983236</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1993,19 +1860,9 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2020,27 +1877,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117965084</v>
+        <v>117980591</v>
       </c>
       <c r="B14" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,37 +1900,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592497</v>
+        <v>592624</v>
       </c>
       <c r="R14" t="n">
-        <v>6983185</v>
+        <v>6982741</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2105,19 +1957,9 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2132,67 +1974,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117965048</v>
+        <v>117964594</v>
       </c>
       <c r="B15" t="n">
-        <v>56502</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592470</v>
+        <v>592544</v>
       </c>
       <c r="R15" t="n">
-        <v>6983180</v>
+        <v>6983091</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2224,7 +2056,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2234,7 +2066,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2249,27 +2081,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117964775</v>
+        <v>117965084</v>
       </c>
       <c r="B16" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2277,34 +2104,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
         <v>592497</v>
       </c>
       <c r="R16" t="n">
-        <v>6983093</v>
+        <v>6983185</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2336,7 +2163,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2346,7 +2173,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2373,15 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117967227</v>
+        <v>117963021</v>
       </c>
       <c r="B17" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,37 +2211,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592271</v>
+        <v>592642</v>
       </c>
       <c r="R17" t="n">
-        <v>6982856</v>
+        <v>6982779</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2448,7 +2275,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2458,7 +2285,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,63 +2312,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117967006</v>
+        <v>117963692</v>
       </c>
       <c r="B18" t="n">
-        <v>56502</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592211</v>
+        <v>592600</v>
       </c>
       <c r="R18" t="n">
-        <v>6983013</v>
+        <v>6982942</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2570,7 +2387,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2580,7 +2397,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2595,27 +2412,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117980684</v>
+        <v>117980604</v>
       </c>
       <c r="B19" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2623,34 +2435,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592455</v>
+        <v>592585</v>
       </c>
       <c r="R19" t="n">
-        <v>6983193</v>
+        <v>6982972</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2709,53 +2529,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117980591</v>
+        <v>117963824</v>
       </c>
       <c r="B20" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592624</v>
+        <v>592573</v>
       </c>
       <c r="R20" t="n">
-        <v>6982741</v>
+        <v>6982989</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2782,9 +2602,19 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2799,65 +2629,65 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117980679</v>
+        <v>117965048</v>
       </c>
       <c r="B21" t="n">
-        <v>90654</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1503</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592361</v>
+        <v>592470</v>
       </c>
       <c r="R21" t="n">
-        <v>6983221</v>
+        <v>6983180</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2884,9 +2714,19 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2901,62 +2741,67 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117980634</v>
+        <v>117967006</v>
       </c>
       <c r="B22" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592165</v>
+        <v>592211</v>
       </c>
       <c r="R22" t="n">
-        <v>6983245</v>
+        <v>6983013</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2986,9 +2831,19 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3003,62 +2858,65 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117980590</v>
+        <v>117980612</v>
       </c>
       <c r="B23" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592274</v>
+        <v>592308</v>
       </c>
       <c r="R23" t="n">
-        <v>6983236</v>
+        <v>6982909</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3117,50 +2975,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117980589</v>
+        <v>117980613</v>
       </c>
       <c r="B24" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592222</v>
+        <v>592247</v>
       </c>
       <c r="R24" t="n">
-        <v>6983283</v>
+        <v>6982930</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3219,15 +3080,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117980704</v>
+        <v>117964679</v>
       </c>
       <c r="B25" t="n">
-        <v>91779</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3235,37 +3091,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>208249</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592312</v>
+        <v>592525</v>
       </c>
       <c r="R25" t="n">
-        <v>6982911</v>
+        <v>6983094</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3292,9 +3148,19 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3309,27 +3175,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117980612</v>
+        <v>117964835</v>
       </c>
       <c r="B26" t="n">
-        <v>56502</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3337,45 +3198,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592308</v>
+        <v>592498</v>
       </c>
       <c r="R26" t="n">
-        <v>6982909</v>
+        <v>6983096</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3402,9 +3260,19 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3419,65 +3287,64 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117980583</v>
+        <v>117963780</v>
       </c>
       <c r="B27" t="n">
-        <v>90469</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592514</v>
+        <v>592591</v>
       </c>
       <c r="R27" t="n">
-        <v>6983143</v>
+        <v>6982977</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3504,9 +3371,19 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3521,70 +3398,64 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117963021</v>
+        <v>117965168</v>
       </c>
       <c r="B28" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592642</v>
+        <v>592400</v>
       </c>
       <c r="R28" t="n">
-        <v>6982779</v>
+        <v>6983226</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3613,7 +3484,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3623,7 +3494,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3638,15 +3509,972 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>117965190</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>592393</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6983227</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>117962937</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>592630</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6982740</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
           <t>Kamilla Andersson</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
+      <c r="AX30" t="inlineStr">
         <is>
           <t>Kamilla Andersson</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>117963859</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>592568</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6982951</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>117964775</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>592497</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6983093</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>117965523</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>592347</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6983195</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>117966861</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>592155</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6983159</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>117966965</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>592168</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6983049</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>117967227</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>592271</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6982856</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>117980634</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lill-Gussjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>592165</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6983245</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10625-2024 artfynd.xlsx
+++ b/artfynd/A 10625-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117967045</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980679</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117964752</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980704</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980583</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980584</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117965382</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980684</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117965787</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117962951</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980589</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1886,6 +1946,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980590</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1983,6 +2048,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980591</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2090,6 +2160,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117964594</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2197,6 +2272,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117965084</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2309,6 +2389,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117963021</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2421,6 +2506,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117963692</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2526,6 +2616,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980604</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2638,6 +2733,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117963824</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2750,6 +2850,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117965048</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2867,6 +2972,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117967006</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2972,6 +3082,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980612</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3077,6 +3192,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980613</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3184,6 +3304,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117964679</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3296,6 +3421,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117964835</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3407,6 +3537,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117963780</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3518,6 +3653,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117965168</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3629,6 +3769,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117965190</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3736,6 +3881,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117962937</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3843,6 +3993,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117963859</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3950,6 +4105,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117964775</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4057,6 +4217,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117965523</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4164,6 +4329,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117966861</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4271,6 +4441,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117966965</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4378,6 +4553,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117967227</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4475,8 +4655,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980634</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 10625-2024 artfynd.xlsx
+++ b/artfynd/A 10625-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,48 +792,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117980679</v>
+        <v>135581557</v>
       </c>
       <c r="B3" t="n">
-        <v>92083</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592361</v>
+        <v>592535</v>
       </c>
       <c r="R3" t="n">
-        <v>6983221</v>
+        <v>6982883</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,31 +873,46 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980679</t>
+          <t>https://artportalen.se/Sighting/135581557</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117964752</v>
+        <v>135581542</v>
       </c>
       <c r="B4" t="n">
-        <v>91962</v>
+        <v>81355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592509</v>
+        <v>592233</v>
       </c>
       <c r="R4" t="n">
-        <v>6983102</v>
+        <v>6982915</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,22 +974,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:37</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:37</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,53 +990,68 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117964752</t>
+          <t>https://artportalen.se/Sighting/135581542</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117980704</v>
+        <v>117980679</v>
       </c>
       <c r="B5" t="n">
-        <v>93197</v>
+        <v>92083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592312</v>
+        <v>592361</v>
       </c>
       <c r="R5" t="n">
-        <v>6982911</v>
+        <v>6983221</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1102,54 +1122,54 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980704</t>
+          <t>https://artportalen.se/Sighting/117980679</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117980583</v>
+        <v>135581554</v>
       </c>
       <c r="B6" t="n">
-        <v>91872</v>
+        <v>90997</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592514</v>
+        <v>592550</v>
       </c>
       <c r="R6" t="n">
-        <v>6983143</v>
+        <v>6982839</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,69 +1209,84 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980583</t>
+          <t>https://artportalen.se/Sighting/135581554</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117980584</v>
+        <v>117964752</v>
       </c>
       <c r="B7" t="n">
-        <v>91872</v>
+        <v>91962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592541</v>
+        <v>592509</v>
       </c>
       <c r="R7" t="n">
-        <v>6983087</v>
+        <v>6983102</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1278,9 +1313,19 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,62 +1340,62 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980584</t>
+          <t>https://artportalen.se/Sighting/117964752</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117965382</v>
+        <v>135581555</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>92027</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592350</v>
+        <v>592550</v>
       </c>
       <c r="R8" t="n">
-        <v>6983237</v>
+        <v>6982838</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,22 +1422,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,53 +1438,68 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117965382</t>
+          <t>https://artportalen.se/Sighting/135581555</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117980684</v>
+        <v>117980704</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592455</v>
+        <v>592312</v>
       </c>
       <c r="R9" t="n">
-        <v>6983193</v>
+        <v>6982911</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1520,16 +1570,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980684</t>
+          <t>https://artportalen.se/Sighting/117980704</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117965787</v>
+        <v>135581567</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>93271</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1537,34 +1587,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592222</v>
+        <v>592510</v>
       </c>
       <c r="R10" t="n">
-        <v>6983253</v>
+        <v>6982896</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,22 +1641,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1621,65 +1661,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117965787</t>
+          <t>https://artportalen.se/Sighting/135581567</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117962951</v>
+        <v>117980583</v>
       </c>
       <c r="B11" t="n">
-        <v>79946</v>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592630</v>
+        <v>592514</v>
       </c>
       <c r="R11" t="n">
-        <v>6982740</v>
+        <v>6983143</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1706,19 +1746,9 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,49 +1763,49 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117962951</t>
+          <t>https://artportalen.se/Sighting/117980583</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117980589</v>
+        <v>117980584</v>
       </c>
       <c r="B12" t="n">
-        <v>79946</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592222</v>
+        <v>592541</v>
       </c>
       <c r="R12" t="n">
-        <v>6983283</v>
+        <v>6983087</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1846,54 +1876,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980589</t>
+          <t>https://artportalen.se/Sighting/117980584</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117980590</v>
+        <v>117965382</v>
       </c>
       <c r="B13" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592274</v>
+        <v>592350</v>
       </c>
       <c r="R13" t="n">
-        <v>6983236</v>
+        <v>6983237</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1920,9 +1950,19 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1937,49 +1977,49 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980590</t>
+          <t>https://artportalen.se/Sighting/117965382</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117980591</v>
+        <v>117980684</v>
       </c>
       <c r="B14" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592624</v>
+        <v>592455</v>
       </c>
       <c r="R14" t="n">
-        <v>6982741</v>
+        <v>6983193</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2050,51 +2090,51 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980591</t>
+          <t>https://artportalen.se/Sighting/117980684</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117964594</v>
+        <v>135581537</v>
       </c>
       <c r="B15" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592544</v>
+        <v>592183</v>
       </c>
       <c r="R15" t="n">
-        <v>6983091</v>
+        <v>6982832</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,22 +2161,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,62 +2181,62 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117964594</t>
+          <t>https://artportalen.se/Sighting/135581537</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117965084</v>
+        <v>135581543</v>
       </c>
       <c r="B16" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592497</v>
+        <v>592287</v>
       </c>
       <c r="R16" t="n">
-        <v>6983185</v>
+        <v>6982924</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,22 +2263,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,70 +2283,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117965084</t>
+          <t>https://artportalen.se/Sighting/135581543</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117963021</v>
+        <v>135581568</v>
       </c>
       <c r="B17" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592642</v>
+        <v>592474</v>
       </c>
       <c r="R17" t="n">
-        <v>6982779</v>
+        <v>6982771</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2350,22 +2365,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,31 +2381,46 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117963021</t>
+          <t>https://artportalen.se/Sighting/135581568</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117963692</v>
+        <v>135581562</v>
       </c>
       <c r="B18" t="n">
-        <v>57953</v>
+        <v>78776</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,39 +2428,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592600</v>
+        <v>592509</v>
       </c>
       <c r="R18" t="n">
-        <v>6982942</v>
+        <v>6982946</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,22 +2482,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2493,31 +2498,46 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117963692</t>
+          <t>https://artportalen.se/Sighting/135581562</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117980604</v>
+        <v>135581566</v>
       </c>
       <c r="B19" t="n">
-        <v>57953</v>
+        <v>78776</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,45 +2545,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592585</v>
+        <v>592471</v>
       </c>
       <c r="R19" t="n">
-        <v>6982972</v>
+        <v>6982995</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2587,12 +2599,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,71 +2615,81 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980604</t>
+          <t>https://artportalen.se/Sighting/135581566</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117963824</v>
+        <v>117965787</v>
       </c>
       <c r="B20" t="n">
-        <v>57141</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592573</v>
+        <v>592222</v>
       </c>
       <c r="R20" t="n">
-        <v>6982989</v>
+        <v>6983253</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2721,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2709,7 +2731,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2724,67 +2746,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117963824</t>
+          <t>https://artportalen.se/Sighting/117965787</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117965048</v>
+        <v>135581538</v>
       </c>
       <c r="B21" t="n">
-        <v>57141</v>
+        <v>79130</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592470</v>
+        <v>592232</v>
       </c>
       <c r="R21" t="n">
-        <v>6983180</v>
+        <v>6982913</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2811,22 +2828,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2837,79 +2844,84 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117965048</t>
+          <t>https://artportalen.se/Sighting/135581538</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117967006</v>
+        <v>135581545</v>
       </c>
       <c r="B22" t="n">
-        <v>57141</v>
+        <v>79130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592211</v>
+        <v>592302</v>
       </c>
       <c r="R22" t="n">
-        <v>6983013</v>
+        <v>6982912</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2933,22 +2945,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:36</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:36</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2959,77 +2961,84 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117967006</t>
+          <t>https://artportalen.se/Sighting/135581545</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117980612</v>
+        <v>135581550</v>
       </c>
       <c r="B23" t="n">
-        <v>57141</v>
+        <v>79130</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592308</v>
+        <v>592533</v>
       </c>
       <c r="R23" t="n">
-        <v>6982909</v>
+        <v>6982844</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3053,12 +3062,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,77 +3078,84 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980612</t>
+          <t>https://artportalen.se/Sighting/135581550</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117980613</v>
+        <v>135581558</v>
       </c>
       <c r="B24" t="n">
-        <v>57141</v>
+        <v>79130</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592247</v>
+        <v>592536</v>
       </c>
       <c r="R24" t="n">
-        <v>6982930</v>
+        <v>6982882</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3163,12 +3179,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3179,53 +3195,68 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980613</t>
+          <t>https://artportalen.se/Sighting/135581558</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117964679</v>
+        <v>117962951</v>
       </c>
       <c r="B25" t="n">
-        <v>58817</v>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208249</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3235,10 +3266,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592525</v>
+        <v>592630</v>
       </c>
       <c r="R25" t="n">
-        <v>6983094</v>
+        <v>6982740</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3270,7 +3301,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3280,7 +3311,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3295,70 +3326,65 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117964679</t>
+          <t>https://artportalen.se/Sighting/117962951</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117964835</v>
+        <v>117980589</v>
       </c>
       <c r="B26" t="n">
-        <v>99035</v>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592498</v>
+        <v>592222</v>
       </c>
       <c r="R26" t="n">
-        <v>6983096</v>
+        <v>6983283</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3385,19 +3411,9 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3412,69 +3428,65 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117964835</t>
+          <t>https://artportalen.se/Sighting/117980589</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117963780</v>
+        <v>117980590</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592591</v>
+        <v>592274</v>
       </c>
       <c r="R27" t="n">
-        <v>6982977</v>
+        <v>6983236</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3501,19 +3513,9 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3528,69 +3530,65 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117963780</t>
+          <t>https://artportalen.se/Sighting/117980590</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117965168</v>
+        <v>117980591</v>
       </c>
       <c r="B28" t="n">
-        <v>99118</v>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592400</v>
+        <v>592624</v>
       </c>
       <c r="R28" t="n">
-        <v>6983226</v>
+        <v>6982741</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3617,19 +3615,9 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3644,66 +3632,62 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117965168</t>
+          <t>https://artportalen.se/Sighting/117980591</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117965190</v>
+        <v>135581541</v>
       </c>
       <c r="B29" t="n">
-        <v>99118</v>
+        <v>79992</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592393</v>
+        <v>592232</v>
       </c>
       <c r="R29" t="n">
-        <v>6983227</v>
+        <v>6982918</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3730,22 +3714,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3756,31 +3730,46 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117965190</t>
+          <t>https://artportalen.se/Sighting/135581541</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117962937</v>
+        <v>135581547</v>
       </c>
       <c r="B30" t="n">
-        <v>79085</v>
+        <v>79992</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3788,34 +3777,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592630</v>
+        <v>592302</v>
       </c>
       <c r="R30" t="n">
-        <v>6982740</v>
+        <v>6982913</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3842,22 +3831,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:58</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:58</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3868,31 +3847,46 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117962937</t>
+          <t>https://artportalen.se/Sighting/135581547</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117963859</v>
+        <v>135581553</v>
       </c>
       <c r="B31" t="n">
-        <v>79085</v>
+        <v>79992</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3900,34 +3894,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592568</v>
+        <v>592549</v>
       </c>
       <c r="R31" t="n">
-        <v>6982951</v>
+        <v>6982838</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3954,22 +3948,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3980,31 +3964,46 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117963859</t>
+          <t>https://artportalen.se/Sighting/135581553</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117964775</v>
+        <v>135581556</v>
       </c>
       <c r="B32" t="n">
-        <v>79085</v>
+        <v>79992</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4012,34 +4011,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592497</v>
+        <v>592556</v>
       </c>
       <c r="R32" t="n">
-        <v>6983093</v>
+        <v>6982851</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4066,22 +4065,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4092,31 +4081,46 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117964775</t>
+          <t>https://artportalen.se/Sighting/135581556</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117965523</v>
+        <v>135581559</v>
       </c>
       <c r="B33" t="n">
-        <v>79085</v>
+        <v>79992</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4124,34 +4128,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592347</v>
+        <v>592520</v>
       </c>
       <c r="R33" t="n">
-        <v>6983195</v>
+        <v>6982868</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4178,22 +4182,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4204,31 +4198,46 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117965523</t>
+          <t>https://artportalen.se/Sighting/135581559</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117966861</v>
+        <v>135581563</v>
       </c>
       <c r="B34" t="n">
-        <v>79085</v>
+        <v>79992</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4236,34 +4245,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592155</v>
+        <v>592507</v>
       </c>
       <c r="R34" t="n">
-        <v>6983159</v>
+        <v>6982959</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4290,22 +4299,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4316,31 +4315,46 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117966861</t>
+          <t>https://artportalen.se/Sighting/135581563</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117966965</v>
+        <v>135581565</v>
       </c>
       <c r="B35" t="n">
-        <v>79085</v>
+        <v>79992</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4348,34 +4362,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>592168</v>
+        <v>592479</v>
       </c>
       <c r="R35" t="n">
-        <v>6983049</v>
+        <v>6982993</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4402,22 +4416,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4428,31 +4432,46 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117966965</t>
+          <t>https://artportalen.se/Sighting/135581565</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117967227</v>
+        <v>117964594</v>
       </c>
       <c r="B36" t="n">
-        <v>79085</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4460,34 +4479,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>592271</v>
+        <v>592544</v>
       </c>
       <c r="R36" t="n">
-        <v>6982856</v>
+        <v>6983091</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4519,7 +4538,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4529,7 +4548,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4555,16 +4574,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117967227</t>
+          <t>https://artportalen.se/Sighting/117964594</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117980634</v>
+        <v>117965084</v>
       </c>
       <c r="B37" t="n">
-        <v>79085</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4572,37 +4591,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592165</v>
+        <v>592497</v>
       </c>
       <c r="R37" t="n">
-        <v>6983245</v>
+        <v>6983185</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4629,9 +4648,19 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4646,18 +4675,3322 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/117965084</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>117963021</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>592642</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6982779</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117963021</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>117963692</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>592600</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6982942</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117963692</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>117980604</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lill-Gussjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>592585</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6982972</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980604</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>117963824</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>592573</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6982989</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117963824</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>117965048</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>592470</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6983180</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117965048</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>117967006</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>592211</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6983013</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117967006</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>117980612</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lill-Gussjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>592308</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6982909</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980612</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>117980613</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lill-Gussjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>592247</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6982930</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980613</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>117964679</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>592525</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6983094</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117964679</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135581548</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>592467</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6982786</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581548</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>117964835</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>592498</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6983096</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117964835</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>117963780</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>592591</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6982977</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117963780</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>117965168</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>592400</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6983226</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117965168</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>117965190</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>592393</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6983227</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117965190</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>117962937</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>592630</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6982740</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117962937</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>117963859</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>592568</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6982951</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117963859</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>117964775</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>592497</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6983093</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117964775</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>117965523</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>592347</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6983195</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117965523</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>117966861</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>592155</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6983159</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117966861</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>117966965</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>592168</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6983049</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117966965</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>117967227</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>592271</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6982856</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117967227</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>117980634</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lill-Gussjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>592165</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6983245</v>
+      </c>
+      <c r="S59" t="n">
+        <v>20</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/117980634</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135581539</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>592232</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6982913</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581539</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135581546</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>592303</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6982913</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581546</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135581549</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>592532</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6982844</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581549</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135581560</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>592507</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6982946</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581560</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135581564</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>592498</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6982966</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581564</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135581551</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>592532</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6982842</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581551</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135581561</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>592506</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6982945</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581561</t>
         </is>
       </c>
     </row>
@@ -4699,6 +8032,35 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10625-2024 artfynd.xlsx
+++ b/artfynd/A 10625-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135581557</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135581542</v>
       </c>
       <c r="B4" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135581554</v>
       </c>
       <c r="B6" t="n">
-        <v>90997</v>
+        <v>91039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>135581555</v>
       </c>
       <c r="B8" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135581567</v>
       </c>
       <c r="B10" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>135581537</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>135581543</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>135581568</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>135581562</v>
       </c>
       <c r="B18" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>135581566</v>
       </c>
       <c r="B19" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>135581538</v>
       </c>
       <c r="B21" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>135581545</v>
       </c>
       <c r="B22" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>135581550</v>
       </c>
       <c r="B23" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>135581558</v>
       </c>
       <c r="B24" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>135581541</v>
       </c>
       <c r="B29" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>135581547</v>
       </c>
       <c r="B30" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>135581553</v>
       </c>
       <c r="B31" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>135581556</v>
       </c>
       <c r="B32" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>135581559</v>
       </c>
       <c r="B33" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>135581563</v>
       </c>
       <c r="B34" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>135581565</v>
       </c>
       <c r="B35" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>135581548</v>
       </c>
       <c r="B47" t="n">
-        <v>58839</v>
+        <v>58844</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>135581539</v>
       </c>
       <c r="B60" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>135581546</v>
       </c>
       <c r="B61" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>135581549</v>
       </c>
       <c r="B62" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>135581560</v>
       </c>
       <c r="B63" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>135581564</v>
       </c>
       <c r="B64" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>135581551</v>
       </c>
       <c r="B65" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>135581561</v>
       </c>
       <c r="B66" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 10625-2024 artfynd.xlsx
+++ b/artfynd/A 10625-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135581557</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135581542</v>
       </c>
       <c r="B4" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135581554</v>
       </c>
       <c r="B6" t="n">
-        <v>91039</v>
+        <v>91066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>135581555</v>
       </c>
       <c r="B8" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135581567</v>
       </c>
       <c r="B10" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>135581537</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>135581543</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>135581568</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>135581562</v>
       </c>
       <c r="B18" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>135581566</v>
       </c>
       <c r="B19" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>135581538</v>
       </c>
       <c r="B21" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>135581545</v>
       </c>
       <c r="B22" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>135581550</v>
       </c>
       <c r="B23" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>135581558</v>
       </c>
       <c r="B24" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>135581541</v>
       </c>
       <c r="B29" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>135581547</v>
       </c>
       <c r="B30" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>135581553</v>
       </c>
       <c r="B31" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>135581556</v>
       </c>
       <c r="B32" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>135581559</v>
       </c>
       <c r="B33" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>135581563</v>
       </c>
       <c r="B34" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>135581565</v>
       </c>
       <c r="B35" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>135581539</v>
       </c>
       <c r="B60" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>135581546</v>
       </c>
       <c r="B61" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>135581549</v>
       </c>
       <c r="B62" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>135581560</v>
       </c>
       <c r="B63" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>135581564</v>
       </c>
       <c r="B64" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>135581551</v>
       </c>
       <c r="B65" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>135581561</v>
       </c>
       <c r="B66" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 10625-2024 artfynd.xlsx
+++ b/artfynd/A 10625-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,48 +792,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117980679</v>
+        <v>135581557</v>
       </c>
       <c r="B3" t="n">
-        <v>92083</v>
+        <v>79107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592361</v>
+        <v>592535</v>
       </c>
       <c r="R3" t="n">
-        <v>6983221</v>
+        <v>6982883</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,31 +873,46 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980679</t>
+          <t>https://artportalen.se/Sighting/135581557</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117964752</v>
+        <v>135581542</v>
       </c>
       <c r="B4" t="n">
-        <v>91962</v>
+        <v>81423</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592509</v>
+        <v>592233</v>
       </c>
       <c r="R4" t="n">
-        <v>6983102</v>
+        <v>6982915</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,22 +974,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:37</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:37</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,53 +990,68 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117964752</t>
+          <t>https://artportalen.se/Sighting/135581542</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117980704</v>
+        <v>117980679</v>
       </c>
       <c r="B5" t="n">
-        <v>93197</v>
+        <v>92083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592312</v>
+        <v>592361</v>
       </c>
       <c r="R5" t="n">
-        <v>6982911</v>
+        <v>6983221</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1102,54 +1122,54 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980704</t>
+          <t>https://artportalen.se/Sighting/117980679</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117980583</v>
+        <v>135581554</v>
       </c>
       <c r="B6" t="n">
-        <v>91872</v>
+        <v>91069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592514</v>
+        <v>592550</v>
       </c>
       <c r="R6" t="n">
-        <v>6983143</v>
+        <v>6982839</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,69 +1209,84 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980583</t>
+          <t>https://artportalen.se/Sighting/135581554</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117980584</v>
+        <v>117964752</v>
       </c>
       <c r="B7" t="n">
-        <v>91872</v>
+        <v>91962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592541</v>
+        <v>592509</v>
       </c>
       <c r="R7" t="n">
-        <v>6983087</v>
+        <v>6983102</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1278,9 +1313,19 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,62 +1340,62 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980584</t>
+          <t>https://artportalen.se/Sighting/117964752</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117965382</v>
+        <v>135581555</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>92101</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592350</v>
+        <v>592550</v>
       </c>
       <c r="R8" t="n">
-        <v>6983237</v>
+        <v>6982838</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,22 +1422,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,53 +1438,68 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117965382</t>
+          <t>https://artportalen.se/Sighting/135581555</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117980684</v>
+        <v>117980704</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592455</v>
+        <v>592312</v>
       </c>
       <c r="R9" t="n">
-        <v>6983193</v>
+        <v>6982911</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1520,16 +1570,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980684</t>
+          <t>https://artportalen.se/Sighting/117980704</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117965787</v>
+        <v>135581567</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>93345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1537,34 +1587,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592222</v>
+        <v>592510</v>
       </c>
       <c r="R10" t="n">
-        <v>6983253</v>
+        <v>6982896</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,22 +1641,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1621,65 +1661,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117965787</t>
+          <t>https://artportalen.se/Sighting/135581567</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117962951</v>
+        <v>117980583</v>
       </c>
       <c r="B11" t="n">
-        <v>79946</v>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592630</v>
+        <v>592514</v>
       </c>
       <c r="R11" t="n">
-        <v>6982740</v>
+        <v>6983143</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1706,19 +1746,9 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,49 +1763,49 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117962951</t>
+          <t>https://artportalen.se/Sighting/117980583</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117980589</v>
+        <v>117980584</v>
       </c>
       <c r="B12" t="n">
-        <v>79946</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592222</v>
+        <v>592541</v>
       </c>
       <c r="R12" t="n">
-        <v>6983283</v>
+        <v>6983087</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1846,54 +1876,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980589</t>
+          <t>https://artportalen.se/Sighting/117980584</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117980590</v>
+        <v>117965382</v>
       </c>
       <c r="B13" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592274</v>
+        <v>592350</v>
       </c>
       <c r="R13" t="n">
-        <v>6983236</v>
+        <v>6983237</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1920,9 +1950,19 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1937,49 +1977,49 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980590</t>
+          <t>https://artportalen.se/Sighting/117965382</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117980591</v>
+        <v>117980684</v>
       </c>
       <c r="B14" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592624</v>
+        <v>592455</v>
       </c>
       <c r="R14" t="n">
-        <v>6982741</v>
+        <v>6983193</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2050,51 +2090,51 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980591</t>
+          <t>https://artportalen.se/Sighting/117980684</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117964594</v>
+        <v>135581537</v>
       </c>
       <c r="B15" t="n">
-        <v>80432</v>
+        <v>79441</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592544</v>
+        <v>592183</v>
       </c>
       <c r="R15" t="n">
-        <v>6983091</v>
+        <v>6982832</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,22 +2161,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,62 +2181,62 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117964594</t>
+          <t>https://artportalen.se/Sighting/135581537</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117965084</v>
+        <v>135581543</v>
       </c>
       <c r="B16" t="n">
-        <v>80432</v>
+        <v>79441</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592497</v>
+        <v>592287</v>
       </c>
       <c r="R16" t="n">
-        <v>6983185</v>
+        <v>6982924</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,22 +2263,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,70 +2283,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117965084</t>
+          <t>https://artportalen.se/Sighting/135581543</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117963021</v>
+        <v>135581568</v>
       </c>
       <c r="B17" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592642</v>
+        <v>592474</v>
       </c>
       <c r="R17" t="n">
-        <v>6982779</v>
+        <v>6982771</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2350,22 +2365,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,31 +2381,46 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117963021</t>
+          <t>https://artportalen.se/Sighting/135581568</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117963692</v>
+        <v>135581562</v>
       </c>
       <c r="B18" t="n">
-        <v>57953</v>
+        <v>78844</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,39 +2428,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592600</v>
+        <v>592509</v>
       </c>
       <c r="R18" t="n">
-        <v>6982942</v>
+        <v>6982946</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,22 +2482,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2493,31 +2498,46 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117963692</t>
+          <t>https://artportalen.se/Sighting/135581562</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117980604</v>
+        <v>135581566</v>
       </c>
       <c r="B19" t="n">
-        <v>57953</v>
+        <v>78844</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,45 +2545,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592585</v>
+        <v>592471</v>
       </c>
       <c r="R19" t="n">
-        <v>6982972</v>
+        <v>6982995</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2587,12 +2599,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,71 +2615,81 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980604</t>
+          <t>https://artportalen.se/Sighting/135581566</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117963824</v>
+        <v>117965787</v>
       </c>
       <c r="B20" t="n">
-        <v>57141</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592573</v>
+        <v>592222</v>
       </c>
       <c r="R20" t="n">
-        <v>6982989</v>
+        <v>6983253</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2721,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2709,7 +2731,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2724,67 +2746,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117963824</t>
+          <t>https://artportalen.se/Sighting/117965787</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117965048</v>
+        <v>135581538</v>
       </c>
       <c r="B21" t="n">
-        <v>57141</v>
+        <v>79198</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592470</v>
+        <v>592232</v>
       </c>
       <c r="R21" t="n">
-        <v>6983180</v>
+        <v>6982913</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2811,22 +2828,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2837,79 +2844,84 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117965048</t>
+          <t>https://artportalen.se/Sighting/135581538</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117967006</v>
+        <v>135581545</v>
       </c>
       <c r="B22" t="n">
-        <v>57141</v>
+        <v>79198</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592211</v>
+        <v>592302</v>
       </c>
       <c r="R22" t="n">
-        <v>6983013</v>
+        <v>6982912</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2933,22 +2945,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:36</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:36</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2959,77 +2961,84 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117967006</t>
+          <t>https://artportalen.se/Sighting/135581545</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117980612</v>
+        <v>135581550</v>
       </c>
       <c r="B23" t="n">
-        <v>57141</v>
+        <v>79198</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592308</v>
+        <v>592533</v>
       </c>
       <c r="R23" t="n">
-        <v>6982909</v>
+        <v>6982844</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3053,12 +3062,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,77 +3078,84 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980612</t>
+          <t>https://artportalen.se/Sighting/135581550</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117980613</v>
+        <v>135581558</v>
       </c>
       <c r="B24" t="n">
-        <v>57141</v>
+        <v>79198</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592247</v>
+        <v>592536</v>
       </c>
       <c r="R24" t="n">
-        <v>6982930</v>
+        <v>6982882</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3163,12 +3179,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3179,53 +3195,68 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117980613</t>
+          <t>https://artportalen.se/Sighting/135581558</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117964679</v>
+        <v>117962951</v>
       </c>
       <c r="B25" t="n">
-        <v>58817</v>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208249</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3235,10 +3266,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592525</v>
+        <v>592630</v>
       </c>
       <c r="R25" t="n">
-        <v>6983094</v>
+        <v>6982740</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3270,7 +3301,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3280,7 +3311,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3295,70 +3326,65 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117964679</t>
+          <t>https://artportalen.se/Sighting/117962951</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117964835</v>
+        <v>117980589</v>
       </c>
       <c r="B26" t="n">
-        <v>99035</v>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592498</v>
+        <v>592222</v>
       </c>
       <c r="R26" t="n">
-        <v>6983096</v>
+        <v>6983283</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3385,19 +3411,9 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3412,69 +3428,65 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117964835</t>
+          <t>https://artportalen.se/Sighting/117980589</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117963780</v>
+        <v>117980590</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592591</v>
+        <v>592274</v>
       </c>
       <c r="R27" t="n">
-        <v>6982977</v>
+        <v>6983236</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3501,19 +3513,9 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3528,69 +3530,65 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117963780</t>
+          <t>https://artportalen.se/Sighting/117980590</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117965168</v>
+        <v>117980591</v>
       </c>
       <c r="B28" t="n">
-        <v>99118</v>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592400</v>
+        <v>592624</v>
       </c>
       <c r="R28" t="n">
-        <v>6983226</v>
+        <v>6982741</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3617,19 +3615,9 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3644,66 +3632,62 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117965168</t>
+          <t>https://artportalen.se/Sighting/117980591</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117965190</v>
+        <v>135581541</v>
       </c>
       <c r="B29" t="n">
-        <v>99118</v>
+        <v>80060</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592393</v>
+        <v>592232</v>
       </c>
       <c r="R29" t="n">
-        <v>6983227</v>
+        <v>6982918</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3730,22 +3714,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3756,31 +3730,46 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117965190</t>
+          <t>https://artportalen.se/Sighting/135581541</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117962937</v>
+        <v>135581547</v>
       </c>
       <c r="B30" t="n">
-        <v>79085</v>
+        <v>80060</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3788,34 +3777,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592630</v>
+        <v>592302</v>
       </c>
       <c r="R30" t="n">
-        <v>6982740</v>
+        <v>6982913</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3842,22 +3831,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:58</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:58</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3868,31 +3847,46 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117962937</t>
+          <t>https://artportalen.se/Sighting/135581547</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117963859</v>
+        <v>135581553</v>
       </c>
       <c r="B31" t="n">
-        <v>79085</v>
+        <v>80060</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3900,34 +3894,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592568</v>
+        <v>592549</v>
       </c>
       <c r="R31" t="n">
-        <v>6982951</v>
+        <v>6982838</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3954,22 +3948,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3980,31 +3964,46 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117963859</t>
+          <t>https://artportalen.se/Sighting/135581553</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117964775</v>
+        <v>135581556</v>
       </c>
       <c r="B32" t="n">
-        <v>79085</v>
+        <v>80060</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4012,34 +4011,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592497</v>
+        <v>592556</v>
       </c>
       <c r="R32" t="n">
-        <v>6983093</v>
+        <v>6982851</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4066,22 +4065,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4092,31 +4081,46 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117964775</t>
+          <t>https://artportalen.se/Sighting/135581556</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117965523</v>
+        <v>135581559</v>
       </c>
       <c r="B33" t="n">
-        <v>79085</v>
+        <v>80060</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4124,34 +4128,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592347</v>
+        <v>592520</v>
       </c>
       <c r="R33" t="n">
-        <v>6983195</v>
+        <v>6982868</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4178,22 +4182,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4204,31 +4198,46 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117965523</t>
+          <t>https://artportalen.se/Sighting/135581559</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117966861</v>
+        <v>135581563</v>
       </c>
       <c r="B34" t="n">
-        <v>79085</v>
+        <v>80060</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4236,34 +4245,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592155</v>
+        <v>592507</v>
       </c>
       <c r="R34" t="n">
-        <v>6983159</v>
+        <v>6982959</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4290,22 +4299,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4316,31 +4315,46 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117966861</t>
+          <t>https://artportalen.se/Sighting/135581563</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117966965</v>
+        <v>135581565</v>
       </c>
       <c r="B35" t="n">
-        <v>79085</v>
+        <v>80060</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4348,34 +4362,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>592168</v>
+        <v>592479</v>
       </c>
       <c r="R35" t="n">
-        <v>6983049</v>
+        <v>6982993</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4402,22 +4416,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4428,31 +4432,46 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117966965</t>
+          <t>https://artportalen.se/Sighting/135581565</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117967227</v>
+        <v>117964594</v>
       </c>
       <c r="B36" t="n">
-        <v>79085</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4460,34 +4479,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>592271</v>
+        <v>592544</v>
       </c>
       <c r="R36" t="n">
-        <v>6982856</v>
+        <v>6983091</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4519,7 +4538,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4529,7 +4548,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4555,16 +4574,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117967227</t>
+          <t>https://artportalen.se/Sighting/117964594</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117980634</v>
+        <v>117965084</v>
       </c>
       <c r="B37" t="n">
-        <v>79085</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4572,37 +4591,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592165</v>
+        <v>592497</v>
       </c>
       <c r="R37" t="n">
-        <v>6983245</v>
+        <v>6983185</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4629,9 +4648,19 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4646,18 +4675,3322 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/117965084</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>117963021</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>592642</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6982779</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117963021</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>117963692</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>592600</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6982942</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117963692</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>117980604</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lill-Gussjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>592585</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6982972</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980604</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>117963824</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>592573</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6982989</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117963824</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>117965048</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>592470</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6983180</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117965048</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>117967006</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>592211</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6983013</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117967006</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>117980612</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lill-Gussjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>592308</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6982909</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980612</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>117980613</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lill-Gussjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>592247</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6982930</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117980613</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>117964679</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>592525</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6983094</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117964679</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135581548</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58844</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>592467</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6982786</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581548</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>117964835</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>592498</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6983096</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117964835</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>117963780</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>592591</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6982977</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117963780</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>117965168</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>592400</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6983226</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117965168</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>117965190</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>592393</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6983227</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117965190</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>117962937</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>592630</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6982740</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117962937</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>117963859</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>592568</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6982951</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117963859</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>117964775</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>592497</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6983093</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117964775</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>117965523</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lillsjöhöjden, Lillsjöhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>592347</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6983195</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117965523</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>117966861</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>592155</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6983159</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117966861</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>117966965</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>592168</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6983049</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117966965</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>117967227</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>592271</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6982856</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117967227</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>117980634</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lill-Gussjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>592165</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6983245</v>
+      </c>
+      <c r="S59" t="n">
+        <v>20</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/117980634</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135581539</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>592232</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6982913</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581539</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135581546</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>592303</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6982913</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581546</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135581549</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>592532</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6982844</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581549</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135581560</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>592507</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6982946</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581560</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135581564</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>592498</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6982966</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581564</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135581551</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>592532</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6982842</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581551</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135581561</v>
+      </c>
+      <c r="B66" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>592506</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6982945</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581561</t>
         </is>
       </c>
     </row>
@@ -4699,6 +8032,35 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10625-2024 artfynd.xlsx
+++ b/artfynd/A 10625-2024 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>135581554</v>
       </c>
       <c r="B6" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>135581555</v>
       </c>
       <c r="B8" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135581567</v>
       </c>
       <c r="B10" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10625-2024 artfynd.xlsx
+++ b/artfynd/A 10625-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135581557</v>
       </c>
       <c r="B3" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135581542</v>
       </c>
       <c r="B4" t="n">
-        <v>81423</v>
+        <v>81425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135581554</v>
       </c>
       <c r="B6" t="n">
-        <v>91071</v>
+        <v>91073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>135581555</v>
       </c>
       <c r="B8" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135581567</v>
       </c>
       <c r="B10" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>135581537</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>135581543</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>135581568</v>
       </c>
       <c r="B17" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>135581562</v>
       </c>
       <c r="B18" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>135581566</v>
       </c>
       <c r="B19" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>135581538</v>
       </c>
       <c r="B21" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>135581545</v>
       </c>
       <c r="B22" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>135581550</v>
       </c>
       <c r="B23" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>135581558</v>
       </c>
       <c r="B24" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>135581541</v>
       </c>
       <c r="B29" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>135581547</v>
       </c>
       <c r="B30" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>135581553</v>
       </c>
       <c r="B31" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>135581556</v>
       </c>
       <c r="B32" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>135581559</v>
       </c>
       <c r="B33" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>135581563</v>
       </c>
       <c r="B34" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>135581565</v>
       </c>
       <c r="B35" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>135581548</v>
       </c>
       <c r="B47" t="n">
-        <v>58844</v>
+        <v>58846</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>135581539</v>
       </c>
       <c r="B60" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>135581546</v>
       </c>
       <c r="B61" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>135581549</v>
       </c>
       <c r="B62" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>135581560</v>
       </c>
       <c r="B63" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>135581564</v>
       </c>
       <c r="B64" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>135581551</v>
       </c>
       <c r="B65" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>135581561</v>
       </c>
       <c r="B66" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 10625-2024 artfynd.xlsx
+++ b/artfynd/A 10625-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135581557</v>
       </c>
       <c r="B3" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135581542</v>
       </c>
       <c r="B4" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135581554</v>
       </c>
       <c r="B6" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>135581555</v>
       </c>
       <c r="B8" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135581567</v>
       </c>
       <c r="B10" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>135581537</v>
       </c>
       <c r="B15" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>135581543</v>
       </c>
       <c r="B16" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>135581568</v>
       </c>
       <c r="B17" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>135581562</v>
       </c>
       <c r="B18" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>135581566</v>
       </c>
       <c r="B19" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>135581538</v>
       </c>
       <c r="B21" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>135581545</v>
       </c>
       <c r="B22" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>135581550</v>
       </c>
       <c r="B23" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>135581558</v>
       </c>
       <c r="B24" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>135581541</v>
       </c>
       <c r="B29" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>135581547</v>
       </c>
       <c r="B30" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>135581553</v>
       </c>
       <c r="B31" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>135581556</v>
       </c>
       <c r="B32" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>135581559</v>
       </c>
       <c r="B33" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>135581563</v>
       </c>
       <c r="B34" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>135581565</v>
       </c>
       <c r="B35" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>135581539</v>
       </c>
       <c r="B60" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>135581546</v>
       </c>
       <c r="B61" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>135581549</v>
       </c>
       <c r="B62" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>135581560</v>
       </c>
       <c r="B63" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>135581564</v>
       </c>
       <c r="B64" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>135581551</v>
       </c>
       <c r="B65" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>135581561</v>
       </c>
       <c r="B66" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 10625-2024 artfynd.xlsx
+++ b/artfynd/A 10625-2024 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>135581554</v>
       </c>
       <c r="B6" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>135581555</v>
       </c>
       <c r="B8" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135581567</v>
       </c>
       <c r="B10" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
